--- a/public/samples/diger-sample-comments.xlsx
+++ b/public/samples/diger-sample-comments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>معرف السجل</t>
   </si>
@@ -28,9 +28,6 @@
     <t>تاريخ ووقت النشر</t>
   </si>
   <si>
-    <t>الرابط المباشر</t>
-  </si>
-  <si>
     <t>عنوان الفيديو أو المنشور</t>
   </si>
   <si>
@@ -52,10 +49,10 @@
     <t>2026-06-10</t>
   </si>
   <si>
+    <t>فيديو تجريبي</t>
+  </si>
+  <si>
     <t>https://example.com/demo-video</t>
-  </si>
-  <si>
-    <t>فيديو تجريبي</t>
   </si>
   <si>
     <t>demo_c1</t>
@@ -573,20 +570,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,199 +607,172 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="7" ht="22" customHeight="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:H7"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="H2" r:id="rId2"/>
-    <hyperlink ref="F3" r:id="rId3"/>
-    <hyperlink ref="H3" r:id="rId4"/>
-    <hyperlink ref="F4" r:id="rId5"/>
-    <hyperlink ref="H4" r:id="rId6"/>
-    <hyperlink ref="F5" r:id="rId7"/>
-    <hyperlink ref="H5" r:id="rId8"/>
-    <hyperlink ref="F6" r:id="rId9"/>
-    <hyperlink ref="H6" r:id="rId10"/>
-    <hyperlink ref="F7" r:id="rId11"/>
-    <hyperlink ref="H7" r:id="rId12"/>
+    <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
   </hyperlinks>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>

--- a/public/samples/diger-sample-comments.xlsx
+++ b/public/samples/diger-sample-comments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>معرف السجل</t>
   </si>
@@ -31,9 +31,6 @@
     <t>عنوان الفيديو أو المنشور</t>
   </si>
   <si>
-    <t>رابط الفيديو أو المنشور</t>
-  </si>
-  <si>
     <t>معرف المصدر الأصلي</t>
   </si>
   <si>
@@ -50,9 +47,6 @@
   </si>
   <si>
     <t>فيديو تجريبي</t>
-  </si>
-  <si>
-    <t>https://example.com/demo-video</t>
   </si>
   <si>
     <t>demo_c1</t>
@@ -137,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -148,12 +142,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
@@ -208,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -219,13 +207,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -570,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -578,11 +560,10 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="48" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,176 +585,147 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>24</v>
       </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" ht="22" customHeight="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
-  <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="G3" r:id="rId2"/>
-    <hyperlink ref="G4" r:id="rId3"/>
-    <hyperlink ref="G5" r:id="rId4"/>
-    <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-  </hyperlinks>
+  <autoFilter ref="A1:G7"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>